--- a/diseases/d228/2010-2014.xlsx
+++ b/diseases/d228/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">

--- a/diseases/d228/2010-2014.xlsx
+++ b/diseases/d228/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
